--- a/word-lists/100-wordlist-Turkish.xlsx
+++ b/word-lists/100-wordlist-Turkish.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Claude word list docs and files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F110CB2-84F9-42E2-BDA3-E8A200D09883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{813F5F5C-C561-4612-B886-40C6C31315A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{6F0E09F3-64E8-48FC-A240-C12BBC8DE4E3}"/>
+    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{225A63BC-C754-4A81-BA0C-B6223F7812F7}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-Turkish" sheetId="1" r:id="rId1"/>
@@ -201,7 +201,7 @@
     <t>zaten</t>
   </si>
   <si>
-    <t>aramak</t>
+    <t>insanlara</t>
   </si>
   <si>
     <t>neden</t>
@@ -243,7 +243,7 @@
     <t>soru</t>
   </si>
   <si>
-    <t>istemek</t>
+    <t>çalışıyor</t>
   </si>
   <si>
     <t>bağlantı</t>
@@ -273,7 +273,7 @@
     <t>taraf</t>
   </si>
   <si>
-    <t>almak</t>
+    <t>günlerde</t>
   </si>
   <si>
     <t>konu</t>
@@ -297,7 +297,7 @@
     <t>şehir</t>
   </si>
   <si>
-    <t>vermek</t>
+    <t>geliyorum</t>
   </si>
   <si>
     <t>çocuk</t>
@@ -324,16 +324,16 @@
     <t>seçmek</t>
   </si>
   <si>
-    <t>bilgi</t>
+    <t>gereksinim</t>
   </si>
   <si>
     <t>hükümet</t>
   </si>
   <si>
-    <t>önemli</t>
-  </si>
-  <si>
-    <t>farklı</t>
+    <t>karşılaştırma</t>
+  </si>
+  <si>
+    <t>değerlendirme</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83208D50-2EE1-47E6-8343-C1CC1A1A9251}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B796C856-FEEF-4865-993B-11BD97751148}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1733,7 +1733,7 @@
         <v>50</v>
       </c>
       <c r="C49">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
